--- a/challenge-2/unstructured_files/Staff_Directory_Extract_Q4_2023.xlsx
+++ b/challenge-2/unstructured_files/Staff_Directory_Extract_Q4_2023.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>j.smith@dwp.gov.uk</t>
+          <t>j.smith@[department].gov.uk</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>a.patel@dwp.gov.uk</t>
+          <t>a.patel@[department].gov.uk</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr"/>
@@ -619,7 +619,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>k.obrien@dwp.gov.uk</t>
+          <t>k.obrien@[department].gov.uk</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>l.chen@dwp.gov.uk</t>
+          <t>l.chen@[department].gov.uk</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>r.mcdonald@dwp.gov.uk</t>
+          <t>r.mcdonald@[department].gov.uk</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>m.johnson@dwp.gov.uk</t>
+          <t>m.johnson@[department].gov.uk</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>e.taylor@dwp.gov.uk</t>
+          <t>e.taylor@[department].gov.uk</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>d.brown@dwp.gov.uk</t>
+          <t>d.brown@[department].gov.uk</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>p.singh@dwp.gov.uk</t>
+          <t>p.singh@[department].gov.uk</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>m.wilson@dwp.gov.uk</t>
+          <t>m.wilson@[department].gov.uk</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>f.khan@dwp.gov.uk</t>
+          <t>f.khan@[department].gov.uk</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>a.davies@dwp.gov.uk</t>
+          <t>a.davies@[department].gov.uk</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>t.robinson@dwp.gov.uk</t>
+          <t>t.robinson@[department].gov.uk</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>n.hughes@dwp.gov.uk</t>
+          <t>n.hughes@[department].gov.uk</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
